--- a/reference/templates/products_crm-template.xlsx
+++ b/reference/templates/products_crm-template.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Легенда" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'products_crm'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'products_crm'!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,7 +62,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -84,6 +84,22 @@
         <patternFill patternType="solid">
           <fgColor rgb="00D9D9D9"/>
           <bgColor rgb="00D9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9D2E9"/>
+          <bgColor rgb="00D9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -449,16 +465,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,48 +493,69 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Джерело</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Точність (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Посилання на товар</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Коротка назва</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Нормалізована категорія</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Тип позиції</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Коментар</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
-  <conditionalFormatting sqref="A2:G2000">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$F2="Перевірено"</formula>
+  <autoFilter ref="A1:J1"/>
+  <conditionalFormatting sqref="A2:J2000">
+    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+      <formula>$I2="Перевірено"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$F2="Не перевірено"</formula>
+    <cfRule type="expression" priority="7" dxfId="3" stopIfTrue="1">
+      <formula>$I2="Виведено з асортименту"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>$F2="Виведено з асортименту"</formula>
+    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+      <formula>$D2&lt;50</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
+      <formula>$D2&gt;=90</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="1" stopIfTrue="0">
+      <formula>$I2="Не перевірено"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Невірний тип позиції" error="Оберіть значення зі списку" type="list">
+    <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Основний товар,Подарунок,Пакування,Послуга"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Невірний статус" error="Оберіть значення зі списку" type="list">
+    <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Не перевірено,Перевірено,Виведено з асортименту"</formula1>
     </dataValidation>
   </dataValidations>
@@ -529,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -556,7 +596,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Жовтий — Не перевірено (потребує вашої перевірки, стан за замовчуванням для нових рядків). Зелений — Перевірено (ви підтвердили). Сірий — Виведено з асортименту.</t>
+          <t>Світлофор уваги, не просто мітка. Зелений — Перевірено (ви підтвердили, найвищий пріоритет). Лаванда — Виведено з асортименту. Червоний — Точність &lt; 50 (не вдалось зіставити взагалі, максимум уваги). Сірий — Точність ≥ 90 (надійно за побудовою, можна не перевіряти детально). Жовтий — Точність 50-89 (ймовірно вірно, глянути побіжно).</t>
         </is>
       </c>
     </row>
@@ -568,7 +608,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Оберіть зі спадного списку в колонці E: Основний товар / Подарунок / Пакування / Послуга. Автоматично попередньо: виручка&gt;0 за період -&gt; Основний товар; виручка=0 -&gt; за словником ключових слів. Ваша правка тут — головне джерело істини.</t>
+          <t>Оберіть зі спадного списку в колонці H: Основний товар / Подарунок / Пакування / Послуга. Автоматично попередньо: виручка&gt;0 за період -&gt; Основний товар; виручка=0 -&gt; за словником ключових слів. Ваша правка тут — головне джерело істини.</t>
         </is>
       </c>
     </row>
@@ -580,7 +620,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Оберіть зі спадного списку в колонці F. Усі нові рядки приходять зі статусом 'Не перевірено' — це проставляє скіл, і лише людина може поміняти на 'Перевірено' чи 'Виведено з асортименту'.</t>
+          <t>Оберіть зі спадного списку в колонці I. Усі нові рядки приходять зі статусом 'Не перевірено' — це проставляє скіл, і лише людина може поміняти на 'Перевірено' чи 'Виведено з асортименту'.</t>
         </is>
       </c>
     </row>
@@ -616,7 +656,43 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>product_crm_id=999999, Rozetka ID=999999, Коротка назва='Тестовий товар', Категорія='Побутова хімія', Тип='Основний товар', Статус='Не перевірено'</t>
+          <t>product_crm_id=999999, Rozetka ID=999999, Джерело='Рекламні кампанії', Точність=100, Посилання='https://rozetka.com.ua/...', Коротка назва='Тестовий товар', Категорія='Побутова хімія', Тип='Основний товар', Статус='Не перевірено'</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Джерело</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Коротке пояснення, звідки взято Rozetka ID: Рекламні кампанії, Вказано вручну в сканері позицій, Зіставлення за назвою товару або Не вдалося зіставити. Довідкова інформація для людини — на колір рядка не впливає.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Посилання на товар</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Пряме посилання на картку Rozetka з події — готове поле, не побудоване вручну.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Точність (%)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Число 0-100 — саме воно фарбує рядок (не Джерело). 100 = ступінь 1-2 (реклама або ручне поле, надійно за побудовою) → сірий. 50-89 = ступінь 3 з кандидатом → жовтий. 0 = кандидата не знайдено → червоний, потребує максимум уваги.</t>
         </is>
       </c>
     </row>

--- a/reference/templates/products_crm-template.xlsx
+++ b/reference/templates/products_crm-template.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Легенда" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'products_crm'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'products_crm'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -473,11 +473,12 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,54 +509,59 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Назва на Rozetka</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Коротка назва</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Нормалізована категорія</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Тип позиції</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Коментар</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
-  <conditionalFormatting sqref="A2:J2000">
-    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
-      <formula>$I2="Перевірено"</formula>
+  <autoFilter ref="A1:K1"/>
+  <conditionalFormatting sqref="A2:K2000">
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>$J2="Перевірено"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="3" stopIfTrue="1">
-      <formula>$I2="Виведено з асортименту"</formula>
+    <cfRule type="expression" priority="7" dxfId="3">
+      <formula>$J2="Виведено з асортименту"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="4" stopIfTrue="1">
+    <cfRule type="expression" priority="8" dxfId="4">
       <formula>$D2&lt;50</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
+    <cfRule type="expression" priority="9" dxfId="2">
       <formula>$D2&gt;=90</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="1" stopIfTrue="0">
-      <formula>$I2="Не перевірено"</formula>
+    <cfRule type="expression" priority="10" dxfId="1">
+      <formula>$J2="Не перевірено"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Основний товар,Подарунок,Пакування,Послуга"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Не перевірено,Перевірено,Виведено з асортименту"</formula1>
     </dataValidation>
   </dataValidations>
@@ -569,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -608,7 +614,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Оберіть зі спадного списку в колонці H: Основний товар / Подарунок / Пакування / Послуга. Автоматично попередньо: виручка&gt;0 за період -&gt; Основний товар; виручка=0 -&gt; за словником ключових слів. Ваша правка тут — головне джерело істини.</t>
+          <t>Оберіть зі спадного списку в колонці I: Основний товар / Подарунок / Пакування / Послуга. Автоматично попередньо: виручка&gt;0 за період -&gt; Основний товар; виручка=0 -&gt; за словником ключових слів. Ваша правка тут — головне джерело істини.</t>
         </is>
       </c>
     </row>
@@ -620,7 +626,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Оберіть зі спадного списку в колонці I. Усі нові рядки приходять зі статусом 'Не перевірено' — це проставляє скіл, і лише людина може поміняти на 'Перевірено' чи 'Виведено з асортименту'.</t>
+          <t>Оберіть зі спадного списку в колонці J. Усі нові рядки приходять зі статусом 'Не перевірено' — це проставляє скіл, і лише людина може поміняти на 'Перевірено' чи 'Виведено з асортименту'.</t>
         </is>
       </c>
     </row>
@@ -656,7 +662,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>product_crm_id=999999, Rozetka ID=999999, Джерело='Рекламні кампанії', Точність=100, Посилання='https://rozetka.com.ua/...', Коротка назва='Тестовий товар', Категорія='Побутова хімія', Тип='Основний товар', Статус='Не перевірено'</t>
+          <t>product_crm_id=999999, Rozetka ID=999999, Джерело='Рекламні кампанії', Точність=100, Посилання='https://rozetka.com.ua/...', Назва на Rozetka='Тестовий товар (Rozetka)', Коротка назва='Тестовий товар', Категорія='Побутова хімія', Тип='Основний товар', Статус='Не перевірено'</t>
         </is>
       </c>
     </row>
@@ -693,6 +699,18 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>Число 0-100 — саме воно фарбує рядок (не Джерело). 100 = ступінь 1-2 (реклама або ручне поле, надійно за побудовою) → сірий. 50-89 = ступінь 3 з кандидатом → жовтий. 0 = кандидата не знайдено → червоний, потребує максимум уваги.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Назва на Rozetka</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Назва картки з тієї ж події позицій/залишків, що й посилання (поле name/href) — готове значення, не побудоване вручну. Порожньо, якщо rozetka_id більше ніде не траплявся. Звірте з «Короткою назвою» з CRM поруч, щоб швидше побачити явно невірний збіг за назвою.</t>
         </is>
       </c>
     </row>
